--- a/tame_output/ON/bt/strategyON_20240311.xlsx
+++ b/tame_output/ON/bt/strategyON_20240311.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>17.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-35.2%</t>
+          <t>-37.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,27 +992,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>468.1%</t>
+          <t>468.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-206.2%</t>
+          <t>-208.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-79.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-81.7%</t>
+          <t>-48.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>104.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>103.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-45.5%</t>
+          <t>-25.8%</t>
         </is>
       </c>
     </row>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-3.987898808686078</v>
+        <v>-4.335212446245434</v>
       </c>
       <c r="E1868" t="n">
-        <v>1.519462311050205</v>
+        <v>1.380536856026463</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.2366917757797393</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-3.993415728530045</v>
+        <v>-4.3407293660894</v>
       </c>
       <c r="E1869" t="n">
-        <v>1.515660463167619</v>
+        <v>1.376735008143877</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.2366917757797393</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-3.998228766995382</v>
+        <v>-4.345542404554737</v>
       </c>
       <c r="E1870" t="n">
-        <v>1.517514223710693</v>
+        <v>1.37858876868695</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.2382384104825251</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-3.996111608271089</v>
+        <v>-4.343425245830445</v>
       </c>
       <c r="E1871" t="n">
-        <v>1.514334782666007</v>
+        <v>1.375409327642264</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.2382384104825251</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-3.995634261692599</v>
+        <v>-4.342947899251955</v>
       </c>
       <c r="E1872" t="n">
-        <v>1.514423619975819</v>
+        <v>1.375498164952076</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.2382384104825251</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-3.994609475385741</v>
+        <v>-4.341923112945097</v>
       </c>
       <c r="E1873" t="n">
-        <v>1.517405050469992</v>
+        <v>1.378479595446249</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.2372136241756675</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-4.01335085564466</v>
+        <v>-4.360664493204016</v>
       </c>
       <c r="E1874" t="n">
-        <v>1.515258801664475</v>
+        <v>1.376333346640732</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.2372136241756675</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-4.026320198429758</v>
+        <v>-4.373633835989115</v>
       </c>
       <c r="E1875" t="n">
-        <v>1.517987084507613</v>
+        <v>1.37906162948387</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.2501829669607661</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-4.019844051636198</v>
+        <v>-4.367157689195555</v>
       </c>
       <c r="E1876" t="n">
-        <v>1.523619293846806</v>
+        <v>1.384693838823063</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.2437068201672065</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-4.016153126679787</v>
+        <v>-4.363466764239144</v>
       </c>
       <c r="E1877" t="n">
-        <v>1.52509566382937</v>
+        <v>1.386170208805627</v>
       </c>
       <c r="F1877" t="n">
         <v>-0.2437068201672065</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-4.008937773807971</v>
+        <v>-4.356251411367328</v>
       </c>
       <c r="E1878" t="n">
-        <v>1.533495002096739</v>
+        <v>1.394569547072996</v>
       </c>
       <c r="F1878" t="n">
         <v>-0.1739285848768247</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-3.957909927726145</v>
+        <v>-4.305223565285502</v>
       </c>
       <c r="E1879" t="n">
-        <v>1.558388695013905</v>
+        <v>1.419463239990163</v>
       </c>
       <c r="F1879" t="n">
         <v>-0.0987192465697237</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-3.884440096058697</v>
+        <v>-4.231753733618054</v>
       </c>
       <c r="E1880" t="n">
-        <v>1.603148329174306</v>
+        <v>1.464222874150563</v>
       </c>
       <c r="F1880" t="n">
         <v>-0.02524941490227528</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-3.804067740594767</v>
+        <v>-4.151381378154124</v>
       </c>
       <c r="E1881" t="n">
-        <v>1.649852492107395</v>
+        <v>1.510927037083652</v>
       </c>
       <c r="F1881" t="n">
         <v>0.05512294056165434</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-3.771135870781916</v>
+        <v>-4.118449508341273</v>
       </c>
       <c r="E1882" t="n">
-        <v>1.655806075130939</v>
+        <v>1.516880620107196</v>
       </c>
       <c r="F1882" t="n">
         <v>0.05512294056165434</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-3.791300512331464</v>
+        <v>-4.13861414989082</v>
       </c>
       <c r="E1883" t="n">
-        <v>1.641068027737144</v>
+        <v>1.502142572713401</v>
       </c>
       <c r="F1883" t="n">
         <v>0.03495829901210701</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-3.732633582309931</v>
+        <v>-4.079947219869287</v>
       </c>
       <c r="E1884" t="n">
-        <v>1.665650589584313</v>
+        <v>1.526725134560571</v>
       </c>
       <c r="F1884" t="n">
         <v>0.1199177674422447</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-3.669564350003591</v>
+        <v>-4.016877987562947</v>
       </c>
       <c r="E1885" t="n">
-        <v>1.693572011135964</v>
+        <v>1.554646556112221</v>
       </c>
       <c r="F1885" t="n">
         <v>0.09140420476001021</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-3.617548836034779</v>
+        <v>-3.964862473594134</v>
       </c>
       <c r="E1886" t="n">
-        <v>1.71836855240989</v>
+        <v>1.579443097386147</v>
       </c>
       <c r="F1886" t="n">
         <v>0.09140420476001021</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-3.441979167113875</v>
+        <v>-3.78929280467323</v>
       </c>
       <c r="E1887" t="n">
-        <v>1.78712119307951</v>
+        <v>1.648195738055767</v>
       </c>
       <c r="F1887" t="n">
         <v>0.09140420476001021</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-3.244709761385876</v>
+        <v>-3.592023398945232</v>
       </c>
       <c r="E1888" t="n">
-        <v>1.881082365535581</v>
+        <v>1.742156910511838</v>
       </c>
       <c r="F1888" t="n">
         <v>0.2886736104880083</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-3.045557654148777</v>
+        <v>-3.392871291708133</v>
       </c>
       <c r="E1889" t="n">
-        <v>1.947692074783738</v>
+        <v>1.808766619759995</v>
       </c>
       <c r="F1889" t="n">
         <v>0.4539961364378217</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-2.819712501429366</v>
+        <v>-3.167026138988722</v>
       </c>
       <c r="E1890" t="n">
-        <v>2.047609208907711</v>
+        <v>1.908683753883968</v>
       </c>
       <c r="F1890" t="n">
         <v>0.4959228120249853</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-2.533437689106672</v>
+        <v>-2.880751326666028</v>
       </c>
       <c r="E1891" t="n">
-        <v>2.163258278392847</v>
+        <v>2.024332823369105</v>
       </c>
       <c r="F1891" t="n">
         <v>0.4959228120249853</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-2.306641862033338</v>
+        <v>-2.653955499592694</v>
       </c>
       <c r="E1892" t="n">
-        <v>2.256610383384289</v>
+        <v>2.117684928360546</v>
       </c>
       <c r="F1892" t="n">
         <v>0.5640367566465299</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-2.02273313110459</v>
+        <v>-2.370046768663945</v>
       </c>
       <c r="E1893" t="n">
-        <v>2.375907579994425</v>
+        <v>2.236982124970682</v>
       </c>
       <c r="F1893" t="n">
         <v>0.5640367566465299</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-1.775745880911638</v>
+        <v>-2.123059518470993</v>
       </c>
       <c r="E1894" t="n">
-        <v>2.46496521767774</v>
+        <v>2.326039762653998</v>
       </c>
       <c r="F1894" t="n">
         <v>0.8110240068394819</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-1.511909013707569</v>
+        <v>-1.859222651266924</v>
       </c>
       <c r="E1895" t="n">
-        <v>2.56061648324646</v>
+        <v>2.421691028222718</v>
       </c>
       <c r="F1895" t="n">
         <v>0.8110240068394819</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-1.244667212839172</v>
+        <v>-1.591980850398527</v>
       </c>
       <c r="E1896" t="n">
-        <v>2.665678643094445</v>
+        <v>2.526753188070703</v>
       </c>
       <c r="F1896" t="n">
         <v>0.8110240068394819</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-0.9688580494386875</v>
+        <v>-1.316171686998043</v>
       </c>
       <c r="E1897" t="n">
-        <v>2.775701993481178</v>
+        <v>2.636776538457436</v>
       </c>
       <c r="F1897" t="n">
         <v>0.9000433151182154</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-0.6997904616717081</v>
+        <v>-1.047104099231063</v>
       </c>
       <c r="E1898" t="n">
-        <v>2.883997534733464</v>
+        <v>2.745072079709721</v>
       </c>
       <c r="F1898" t="n">
         <v>1.169110902885195</v>
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.439833833167123</v>
+        <v>3.453364212330688</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-0.4458726840092965</v>
+        <v>-0.4647991900161103</v>
       </c>
       <c r="E1899" t="n">
-        <v>2.972304329636676</v>
+        <v>2.96473372723395</v>
       </c>
       <c r="F1899" t="n">
-        <v>1.423028680547607</v>
+        <v>1.751415812100148</v>
       </c>
       <c r="G1899" t="n">
-        <v>4.004827035882706</v>
+        <v>4.20185931481423</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240311.xlsx
+++ b/tame_output/ON/bt/strategyON_20240311.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-40.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1002,22 +1002,22 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>468.4%</t>
+          <t>467.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-208.1%</t>
+          <t>-239.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,27 +1165,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-92.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-80.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>104.1%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.6%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-44.9%</t>
         </is>
       </c>
     </row>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.453364212330688</v>
+        <v>3.45336421233069</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-0.4647991900161103</v>
+        <v>-0.7830441609082672</v>
       </c>
       <c r="E1899" t="n">
-        <v>2.96473372723395</v>
+        <v>2.837435738877087</v>
       </c>
       <c r="F1899" t="n">
-        <v>1.751415812100148</v>
+        <v>1.433170841207991</v>
       </c>
       <c r="G1899" t="n">
-        <v>4.20185931481423</v>
+        <v>4.010912332278937</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240311.xlsx
+++ b/tame_output/ON/bt/strategyON_20240311.xlsx
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>

--- a/tame_output/ON/bt/strategyON_20240311.xlsx
+++ b/tame_output/ON/bt/strategyON_20240311.xlsx
@@ -605,12 +605,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>19.6%</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-41.4%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>99.9%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>466.2%</t>
+          <t>463.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-238.8%</t>
+          <t>-204.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-92.3%</t>
+          <t>-78.4%</t>
         </is>
       </c>
     </row>
@@ -1318,22 +1318,22 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-133.4%</t>
+          <t>-121.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-4.335212446245434</v>
+        <v>-3.987898808686078</v>
       </c>
       <c r="E1868" t="n">
-        <v>1.380536856026463</v>
+        <v>1.519462311050205</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.2366917757797393</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-4.644812195132987</v>
+        <v>-4.300723607931058</v>
       </c>
       <c r="E1869" t="n">
-        <v>1.255101876526442</v>
+        <v>1.392737311407214</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.2366917757797393</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-4.649625233598324</v>
+        <v>-4.305536646396395</v>
       </c>
       <c r="E1870" t="n">
-        <v>1.256955637069516</v>
+        <v>1.394591071950288</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.2382384104825251</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-4.647508074874032</v>
+        <v>-4.303419487672103</v>
       </c>
       <c r="E1871" t="n">
-        <v>1.253776196024829</v>
+        <v>1.391411630905601</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.2382384104825251</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-4.647030728295542</v>
+        <v>-4.302942141093613</v>
       </c>
       <c r="E1872" t="n">
-        <v>1.253865033334641</v>
+        <v>1.391500468215413</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.2382384104825251</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-4.646005941988684</v>
+        <v>-4.301917354786755</v>
       </c>
       <c r="E1873" t="n">
-        <v>1.256846463828815</v>
+        <v>1.394481898709587</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.2372136241756675</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-4.664747322247603</v>
+        <v>-4.320658735045674</v>
       </c>
       <c r="E1874" t="n">
-        <v>1.254700215023297</v>
+        <v>1.392335649904069</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.2372136241756675</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-4.677716665032702</v>
+        <v>-4.333628077830772</v>
       </c>
       <c r="E1875" t="n">
-        <v>1.257428497866435</v>
+        <v>1.395063932747207</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.2501829669607661</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-4.671240518239142</v>
+        <v>-4.327151931037212</v>
       </c>
       <c r="E1876" t="n">
-        <v>1.263060707205628</v>
+        <v>1.4006961420864</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.2437068201672065</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-4.667549593282731</v>
+        <v>-4.323461006080801</v>
       </c>
       <c r="E1877" t="n">
-        <v>1.264537077188193</v>
+        <v>1.402172512068965</v>
       </c>
       <c r="F1877" t="n">
         <v>-0.2437068201672065</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-4.660334240410915</v>
+        <v>-4.316245653208985</v>
       </c>
       <c r="E1878" t="n">
-        <v>1.272936415455561</v>
+        <v>1.410571850336334</v>
       </c>
       <c r="F1878" t="n">
         <v>-0.1739285848768247</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-4.609306394329089</v>
+        <v>-4.265217807127159</v>
       </c>
       <c r="E1879" t="n">
-        <v>1.297830108372728</v>
+        <v>1.4354655432535</v>
       </c>
       <c r="F1879" t="n">
         <v>-0.0987192465697237</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-4.535836562661641</v>
+        <v>-4.191747975459711</v>
       </c>
       <c r="E1880" t="n">
-        <v>1.342589742533128</v>
+        <v>1.4802251774139</v>
       </c>
       <c r="F1880" t="n">
         <v>-0.02524941490227528</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-4.455464207197711</v>
+        <v>-4.111375619995781</v>
       </c>
       <c r="E1881" t="n">
-        <v>1.389293905466217</v>
+        <v>1.526929340346989</v>
       </c>
       <c r="F1881" t="n">
         <v>0.05512294056165434</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-4.42253233738486</v>
+        <v>-4.07844375018293</v>
       </c>
       <c r="E1882" t="n">
-        <v>1.395247488489761</v>
+        <v>1.532882923370533</v>
       </c>
       <c r="F1882" t="n">
         <v>0.05512294056165434</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-4.442696978934407</v>
+        <v>-4.098608391732477</v>
       </c>
       <c r="E1883" t="n">
-        <v>1.380509441095966</v>
+        <v>1.518144875976738</v>
       </c>
       <c r="F1883" t="n">
         <v>0.03495829901210701</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-4.384030048912874</v>
+        <v>-4.039941461710944</v>
       </c>
       <c r="E1884" t="n">
-        <v>1.405092002943136</v>
+        <v>1.542727437823908</v>
       </c>
       <c r="F1884" t="n">
         <v>0.1199177674422447</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-4.320960816606534</v>
+        <v>-3.976872229404604</v>
       </c>
       <c r="E1885" t="n">
-        <v>1.433013424494786</v>
+        <v>1.570648859375559</v>
       </c>
       <c r="F1885" t="n">
         <v>0.09140420476001021</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-4.268945302637722</v>
+        <v>-3.924856715435792</v>
       </c>
       <c r="E1886" t="n">
-        <v>1.457809965768712</v>
+        <v>1.595445400649484</v>
       </c>
       <c r="F1886" t="n">
         <v>0.09140420476001021</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-4.093375633716818</v>
+        <v>-3.749287046514888</v>
       </c>
       <c r="E1887" t="n">
-        <v>1.526562606438332</v>
+        <v>1.664198041319104</v>
       </c>
       <c r="F1887" t="n">
         <v>0.09140420476001021</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-3.896106227988819</v>
+        <v>-3.55201764078689</v>
       </c>
       <c r="E1888" t="n">
-        <v>1.620523778894404</v>
+        <v>1.758159213775176</v>
       </c>
       <c r="F1888" t="n">
         <v>0.2886736104880083</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-3.69695412075172</v>
+        <v>-3.352865533549791</v>
       </c>
       <c r="E1889" t="n">
-        <v>1.68713348814256</v>
+        <v>1.824768923023333</v>
       </c>
       <c r="F1889" t="n">
         <v>0.4539961364378217</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-3.47110896803231</v>
+        <v>-3.12702038083038</v>
       </c>
       <c r="E1890" t="n">
-        <v>1.787050622266533</v>
+        <v>1.924686057147305</v>
       </c>
       <c r="F1890" t="n">
         <v>0.4959228120249853</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-3.184834155709615</v>
+        <v>-2.840745568507685</v>
       </c>
       <c r="E1891" t="n">
-        <v>1.90269969175167</v>
+        <v>2.040335126632442</v>
       </c>
       <c r="F1891" t="n">
         <v>0.4959228120249853</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-2.958038328636281</v>
+        <v>-2.613949741434352</v>
       </c>
       <c r="E1892" t="n">
-        <v>1.996051796743111</v>
+        <v>2.133687231623883</v>
       </c>
       <c r="F1892" t="n">
         <v>0.5640367566465299</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-2.674129597707533</v>
+        <v>-2.330041010505603</v>
       </c>
       <c r="E1893" t="n">
-        <v>2.115348993353247</v>
+        <v>2.252984428234019</v>
       </c>
       <c r="F1893" t="n">
         <v>0.5640367566465299</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-2.427142347514581</v>
+        <v>-2.083053760312651</v>
       </c>
       <c r="E1894" t="n">
-        <v>2.204406631036563</v>
+        <v>2.342042065917335</v>
       </c>
       <c r="F1894" t="n">
         <v>0.8110240068394819</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-2.163305480310512</v>
+        <v>-1.819216893108582</v>
       </c>
       <c r="E1895" t="n">
-        <v>2.300057896605283</v>
+        <v>2.437693331486055</v>
       </c>
       <c r="F1895" t="n">
         <v>0.8110240068394819</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-1.896063679442115</v>
+        <v>-1.551975092240185</v>
       </c>
       <c r="E1896" t="n">
-        <v>2.405120056453268</v>
+        <v>2.54275549133404</v>
       </c>
       <c r="F1896" t="n">
         <v>0.8110240068394819</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-1.62025451604163</v>
+        <v>-1.2761659288397</v>
       </c>
       <c r="E1897" t="n">
-        <v>2.51514340684</v>
+        <v>2.652778841720773</v>
       </c>
       <c r="F1897" t="n">
         <v>0.9000433151182154</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-1.351186928274651</v>
+        <v>-1.007098341072721</v>
       </c>
       <c r="E1898" t="n">
-        <v>2.623438948092286</v>
+        <v>2.761074382973058</v>
       </c>
       <c r="F1898" t="n">
         <v>1.169110902885195</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.45336421233069</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-1.087126989951855</v>
+        <v>-0.7430384027499251</v>
       </c>
       <c r="E1899" t="n">
-        <v>2.715802607259652</v>
+        <v>2.853438042140425</v>
       </c>
       <c r="F1899" t="n">
         <v>1.433170841207991</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.494083456397527</v>
+        <v>3.476330134597721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-0.7720639387827006</v>
+        <v>-0.4247495481611067</v>
       </c>
       <c r="E1900" t="n">
-        <v>2.839040794067013</v>
+        <v>2.977966550315651</v>
       </c>
       <c r="F1900" t="n">
         <v>1.433170841207991</v>
